--- a/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03-A16_통합요청표_20261028_담당자반영.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03-A16_통합요청표_20261028_담당자반영.xlsx
@@ -523,11 +523,10 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NQA 갱신심사 2026-11-19~20 (ISO 14001:2015 갱신만 진행, 2026 전환 미진행: 사용자 결정 2026-10-28). 담당 실명은 지정되지 않아 각 시트 제목의 [담당자 지정 후 이름 기재]로 비어 있습니다. 시행 전 기록은 "미확인", 소급 작성 금지. 노란 칸이 입력 칸이며 시트 이름을 누르면 해당 시트로 이동합니다. A-01·A-02는 완료(인증서 스캔본 확보, NQA 유선 회신)로 별도 표(ISO14001_증빙수집요청표_20261028_v4.xlsx)에 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>NQA 갱신심사 2026-11-19~20 (ISO 14001:2015 갱신만 진행, 2026 전환 미진행: 사용자 결정 2026-10-28). 담당자는 2026-10-28 담당자 지정표 기준으로 각 시트 제목에 기재했고, A-01~A-14 대체자는 이광재 부장입니다(A-15·A-16 대체자는 미지정). 시행 전 기록은 "미확인", 소급 작성 금지. 노란 칸이 입력 칸이며 시트 이름을 누르면 해당 시트로 이동합니다. A-01·A-02는 완료(인증서 스캔본 확보, NQA 유선 회신)로 별도 표(ISO14001_증빙수집요청표_20261028_v4.xlsx)에 있습니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -571,7 +570,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-10-29</t>
+          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-29</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -596,7 +595,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-10-30</t>
+          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-30</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -621,7 +620,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-02</t>
+          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-02</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -646,7 +645,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-04</t>
+          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-04</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -671,7 +670,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>A-07 최근 1년 폐기물 처리·보관·위탁 증빙 — 담당 역할: 환경/총무 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-04</t>
+          <t>A-07 최근 1년 폐기물 처리·보관·위탁 증빙 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-04</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -721,7 +720,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>A-08 화학물질·MSDS·용기표시·누출관리 — 담당 역할: 환경/생산 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-05</t>
+          <t>A-08 화학물질·MSDS·용기표시·누출관리 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-05</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -771,7 +770,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-06</t>
+          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -846,7 +845,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-06</t>
+          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -921,7 +920,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-10</t>
+          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -996,7 +995,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-12</t>
+          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: 김흥수 이사 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1046,7 +1045,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-12</t>
+          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1096,7 +1095,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-10</t>
+          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1146,7 +1145,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-16</t>
+          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 권고일 2026-11-16</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1221,7 +1220,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-17</t>
+          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 권고일 2026-11-17</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1329,7 +1328,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1626,7 +1624,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 권고일 2026-11-06</t>
+          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1635,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1991,7 +1988,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2230,7 +2226,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2477,7 +2472,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: 박철호 부장 · 권고일 2026-11-06</t>
+          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2483,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2840,7 +2834,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3077,7 +3070,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3248,7 +3240,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: 박철호 부장 · 권고일 2026-11-10</t>
+          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3251,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3572,7 +3563,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4294,7 +4284,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4542,7 +4531,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
@@ -4592,7 +4580,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -4642,7 +4629,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
@@ -4685,7 +4671,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -4766,7 +4751,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: 김흥수 이사 · 권고일 2026-11-12</t>
+          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: 김흥수 이사 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4762,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5081,7 +5065,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5415,7 +5398,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: 박철호 부장 · 권고일 2026-11-12</t>
+          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5409,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5738,7 +5720,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5924,7 +5905,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 권고일 2026-11-10</t>
+          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5916,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6209,7 +6189,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6419,7 +6398,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6689,7 +6667,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7252,7 +7229,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7460,7 +7436,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7755,7 +7730,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: 박철호 부장 · 권고일 2026-10-29</t>
+          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7741,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -8117,7 +8091,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -8653,7 +8626,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 권고일 2026-10-30</t>
+          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8637,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -9048,7 +9020,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 권고일 2026-11-02</t>
+          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-02</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9031,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -9614,7 +9585,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: 박철호 부장 · 권고일 2026-11-04</t>
+          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-04</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9596,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10077,7 +10047,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-07 최근 1년 폐기물 처리·보관·위탁 증빙 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 권고일 2026-11-04</t>
+          <t>A-07 최근 1년 폐기물 처리·보관·위탁 증빙 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-04</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10058,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10441,7 +10410,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10713,7 +10681,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-08 화학물질·MSDS·용기표시·누출관리 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 권고일 2026-11-05</t>
+          <t>A-08 화학물질·MSDS·용기표시·누출관리 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-05</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10692,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03-A16_통합요청표_20261028_담당자반영.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03-A16_통합요청표_20261028_담당자반영.xlsx
@@ -523,10 +523,11 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NQA 갱신심사 2026-11-19~20 (ISO 14001:2015 갱신만 진행, 2026 전환 미진행: 사용자 결정 2026-10-28). 담당자는 2026-10-28 담당자 지정표 기준으로 각 시트 제목에 기재했고, A-01~A-14 대체자는 이광재 부장입니다(A-15·A-16 대체자는 미지정). 시행 전 기록은 "미확인", 소급 작성 금지. 노란 칸이 입력 칸이며 시트 이름을 누르면 해당 시트로 이동합니다. A-01·A-02는 완료(인증서 스캔본 확보, NQA 유선 회신)로 별도 표(ISO14001_증빙수집요청표_20261028_v4.xlsx)에 있습니다.</t>
-        </is>
-      </c>
-    </row>
+          <t>NQA 갱신심사 2026-11-19~20 (ISO 14001:2015 갱신만 진행, 2026 전환 미진행: 사용자 결정 2026-10-28). 담당자는 2026-10-28 담당자 지정표 기준으로 각 시트 제목에 기재했고, A-03~A-16 대체자는 이광재 부장입니다. 시행 전 기록은 "미확인", 소급 작성 금지. 노란 칸이 입력 칸이며 시트 이름을 누르면 해당 시트로 이동합니다. A-01·A-02는 완료(인증서 스캔본 확보, NQA 유선 회신)로 별도 표(ISO14001_증빙수집요청표_20261028_v4.xlsx)에 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1146,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 권고일 2026-11-16</t>
+          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 대체자: 이광재 부장 · 권고일 2026-11-16</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1220,7 +1221,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 권고일 2026-11-17</t>
+          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-17</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1328,6 +1329,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1635,6 +1637,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1988,6 +1991,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2226,6 +2230,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2483,6 +2488,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2834,6 +2840,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3070,6 +3077,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3251,6 +3259,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3563,6 +3572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4284,6 +4294,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4531,6 +4542,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
@@ -4580,6 +4592,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -4629,6 +4642,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
@@ -4671,6 +4685,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -4762,6 +4777,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5065,6 +5081,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5409,6 +5426,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5720,6 +5738,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5916,6 +5935,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6189,6 +6209,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6387,7 +6408,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 권고일 2026-11-16</t>
+          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 대체자: 이광재 부장 · 권고일 2026-11-16</t>
         </is>
       </c>
     </row>
@@ -6398,6 +6419,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6667,6 +6689,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7229,6 +7252,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7425,7 +7449,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 권고일 2026-11-17</t>
+          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-17</t>
         </is>
       </c>
     </row>
@@ -7436,6 +7460,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7741,6 +7766,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -8091,6 +8117,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -8637,6 +8664,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -9031,6 +9059,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -9596,6 +9625,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10058,6 +10088,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10410,6 +10441,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10692,6 +10724,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
